--- a/TESTES.xlsx
+++ b/TESTES.xlsx
@@ -489,7 +489,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -750,12 +750,12 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>notebook, Google Chrome, wifi</t>
+          <t>Verificacao de codigo (app.tsx + api.ts) — nao testado em dispositivo fisico nesta data.</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>O overlay ainda nao some pois nao ha verificacao.</t>
+          <t>Overlay liga com isAnalyzing=true (app.tsx) e desliga ao final de handleCaptured. Como analyzeImage() (api.ts) nunca rejeita — todo erro vira AnalyzeResponse com type: error em vez de excecao — esse desligamento e incondicional, nao depende de um bloco finally. Confirmado por leitura de codigo; recomenda-se validacao manual em dispositivo real durante o fechamento do ticket 03 (testes de PWA).</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -1043,7 +1043,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -1281,7 +1281,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -1604,7 +1604,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -1859,7 +1859,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -2063,7 +2063,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -2318,7 +2318,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -2505,7 +2505,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
@@ -2641,7 +2641,7 @@
     <row r="2" ht="6" customHeight="1" s="17"/>
     <row r="3" ht="6" customHeight="1" s="17"/>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="0" t="inlineStr"/>
       <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ACAO</t>
